--- a/xlsx/data_fusion_accuracy_assessment.xlsx
+++ b/xlsx/data_fusion_accuracy_assessment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\percy\Documents\studies\visual_studio_code\PhD-chapter2-data-fusion-full-diurnal-lst\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8A2D66F-C393-409E-9A09-2A1B1F846091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36F87072-50B9-4FD8-8474-A604CAA6D8A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9F921EDC-B147-402C-B34E-569BC163062E}"/>
+    <workbookView xWindow="38280" yWindow="6720" windowWidth="29040" windowHeight="15720" xr2:uid="{9F921EDC-B147-402C-B34E-569BC163062E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -652,6 +652,18 @@
       <c r="C8" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="D8">
+        <v>-9.4167640271654845E-3</v>
+      </c>
+      <c r="E8">
+        <v>2.2141053819471349E-2</v>
+      </c>
+      <c r="F8">
+        <v>-0.20533426642564279</v>
+      </c>
+      <c r="G8">
+        <v>0.14146825575861849</v>
+      </c>
       <c r="H8" t="str">
         <f t="shared" si="0"/>
         <v>STARFM_2021/12/12</v>
@@ -667,6 +679,18 @@
       <c r="C9" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="D9">
+        <v>-8.9054055374383316E-3</v>
+      </c>
+      <c r="E9">
+        <v>2.4086453909355252E-2</v>
+      </c>
+      <c r="F9">
+        <v>-0.25969115367149648</v>
+      </c>
+      <c r="G9">
+        <v>8.4261221250019516E-2</v>
+      </c>
       <c r="H9" t="str">
         <f t="shared" si="0"/>
         <v>STARFM_2023/02/09</v>
@@ -682,6 +706,18 @@
       <c r="C10" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="D10">
+        <v>-7.7635886561087828E-3</v>
+      </c>
+      <c r="E10">
+        <v>2.1182604758866519E-2</v>
+      </c>
+      <c r="F10">
+        <v>-0.218925568425479</v>
+      </c>
+      <c r="G10">
+        <v>0.12363439771362909</v>
+      </c>
       <c r="H10" t="str">
         <f t="shared" si="0"/>
         <v>FSDAF_2021/12/12</v>
@@ -696,6 +732,18 @@
       </c>
       <c r="C11" s="1" t="s">
         <v>7</v>
+      </c>
+      <c r="D11">
+        <v>-7.1573998256915143E-3</v>
+      </c>
+      <c r="E11">
+        <v>2.320332926434528E-2</v>
+      </c>
+      <c r="F11">
+        <v>-0.27244698115643329</v>
+      </c>
+      <c r="G11">
+        <v>7.5640035290842886E-2</v>
       </c>
       <c r="H11" t="str">
         <f t="shared" si="0"/>
